--- a/artfynd/A 21026-2026 artfynd.xlsx
+++ b/artfynd/A 21026-2026 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>134024861</v>
       </c>
       <c r="B4" t="n">
-        <v>75454</v>
+        <v>75461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>134025591</v>
       </c>
       <c r="B5" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>134025671</v>
       </c>
       <c r="B6" t="n">
-        <v>75454</v>
+        <v>75461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>134025957</v>
       </c>
       <c r="B8" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>134026359</v>
       </c>
       <c r="B9" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 21026-2026 artfynd.xlsx
+++ b/artfynd/A 21026-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134026170</v>
+        <v>134024346</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sättern, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408739</v>
+        <v>408729</v>
       </c>
       <c r="R2" t="n">
-        <v>6638547</v>
+        <v>6638622</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134024712</v>
+        <v>134024515</v>
       </c>
       <c r="B3" t="n">
-        <v>58839</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408675</v>
+        <v>408703</v>
       </c>
       <c r="R3" t="n">
-        <v>6638663</v>
+        <v>6638631</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,11 +892,11 @@
         <v>134024861</v>
       </c>
       <c r="B4" t="n">
-        <v>75461</v>
+        <v>75468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1010,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134025591</v>
+        <v>134025671</v>
       </c>
       <c r="B5" t="n">
-        <v>79985</v>
+        <v>75468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1080,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134025671</v>
+        <v>134025591</v>
       </c>
       <c r="B6" t="n">
-        <v>75461</v>
+        <v>79992</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1187,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1197,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,54 +1210,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134025247</v>
+        <v>134025957</v>
       </c>
       <c r="B7" t="n">
-        <v>5201</v>
+        <v>79992</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sättern, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>408609</v>
+        <v>408791</v>
       </c>
       <c r="R7" t="n">
-        <v>6638697</v>
+        <v>6638717</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134025957</v>
+        <v>134026359</v>
       </c>
       <c r="B8" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408791</v>
+        <v>408825</v>
       </c>
       <c r="R8" t="n">
-        <v>6638717</v>
+        <v>6638684</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,45 +1424,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134026359</v>
+        <v>134026170</v>
       </c>
       <c r="B9" t="n">
-        <v>79985</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sättern, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>408825</v>
+        <v>408739</v>
       </c>
       <c r="R9" t="n">
-        <v>6638684</v>
+        <v>6638547</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,7 +1508,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1527,7 +1518,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,6 +1542,229 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134025247</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sättern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>408609</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6638697</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134024712</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sättern, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>408675</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6638663</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
